--- a/weather.xlsx
+++ b/weather.xlsx
@@ -446,17 +446,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>34,1</t>
+          <t>36,3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -468,7 +468,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>27,1</t>
+          <t>32,6</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -478,7 +478,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -490,17 +490,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>29,3</t>
+          <t>30,5</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -512,12 +512,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30,3</t>
+          <t>37,8</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -534,17 +534,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>27,7</t>
+          <t>33,1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -556,12 +556,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25,5</t>
+          <t>30,9</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -578,12 +578,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>23,9</t>
+          <t>28,3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -600,17 +600,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>27,8</t>
+          <t>32,2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -622,12 +622,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>27,7</t>
+          <t>32,4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -644,12 +644,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>26,1</t>
+          <t>32,5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>31,8</t>
+          <t>37,9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -688,17 +688,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>36,5</t>
+          <t>41,9</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>26,5</t>
+          <t>31,1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -732,17 +732,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>28,7</t>
+          <t>34,3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>26,8</t>
+          <t>31,7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -776,17 +776,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>35,3</t>
+          <t>38,2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>29,9</t>
+          <t>31,6</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -820,12 +820,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>28,5</t>
+          <t>30,9</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32,2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -864,17 +864,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>28,9</t>
+          <t>33,5</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -886,17 +886,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>28,8</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -908,12 +908,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>28,7</t>
+          <t>31,8</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>26,9</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>29,9</t>
+          <t>33,3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -974,17 +974,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>29,4</t>
+          <t>35,4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>31,4</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1018,17 +1018,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>29,9</t>
+          <t>36,3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -1040,12 +1040,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>26,9</t>
+          <t>31,6</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>27,3</t>
+          <t>29,4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>35,5</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1106,17 +1106,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>29,4</t>
+          <t>27,9</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -1128,17 +1128,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>26,5</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -1150,17 +1150,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>28,5</t>
+          <t>32,7</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -468,7 +468,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>32,6</t>
+          <t>32,7</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -512,7 +512,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>37,8</t>
+          <t>37,6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>33,1</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>28,3</t>
+          <t>28,4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>32,2</t>
+          <t>31,9</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>32,4</t>
+          <t>32,3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>32,5</t>
+          <t>33,1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>41,9</t>
+          <t>41,6</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>31,1</t>
+          <t>31,2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>34,3</t>
+          <t>33,7</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>31,7</t>
+          <t>31,8</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>38,2</t>
+          <t>38,5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>31,6</t>
+          <t>31,8</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>30,9</t>
+          <t>30,8</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>32,2</t>
+          <t>31,8</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>33,5</t>
+          <t>33,9</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>35,6</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>31,8</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>32,2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>33,3</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>35,4</t>
+          <t>35,3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>33,4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>36,3</t>
+          <t>36,7</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>31,6</t>
+          <t>31,3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>29,4</t>
+          <t>29,3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>40,3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>27,9</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27,4</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>32,7</t>
+          <t>32,8</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -446,7 +446,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>36,3</t>
+          <t>35,5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -468,7 +468,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>32,7</t>
+          <t>32,4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -512,7 +512,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>37,6</t>
+          <t>38,2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>33,5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -556,7 +556,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>30,9</t>
+          <t>31,4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>28,4</t>
+          <t>28,2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>31,9</t>
+          <t>31,8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>32,3</t>
+          <t>32,8</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>33,1</t>
+          <t>33,2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>37,9</t>
+          <t>38,1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>41,6</t>
+          <t>41,9</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>31,2</t>
+          <t>31,5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>33,7</t>
+          <t>34,3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>38,5</t>
+          <t>39,1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>31,8</t>
+          <t>31,7</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>30,8</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>31,8</t>
+          <t>32,4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>33,9</t>
+          <t>33,8</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>35,6</t>
+          <t>34,2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32,4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>32,2</t>
+          <t>31,6</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33,7</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>35,3</t>
+          <t>35,9</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>33,4</t>
+          <t>33,2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>36,7</t>
+          <t>36,9</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>31,3</t>
+          <t>32,7</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>29,3</t>
+          <t>29,1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27,9</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>27,4</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>32,8</t>
+          <t>32,9</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -446,7 +446,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>35,5</t>
+          <t>34,8</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -468,7 +468,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>32,4</t>
+          <t>32,5</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30,5</t>
+          <t>30,2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -512,7 +512,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>38,2</t>
+          <t>38,5</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>33,5</t>
+          <t>33,1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -556,7 +556,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>31,4</t>
+          <t>31,1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>28,2</t>
+          <t>28,3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>31,8</t>
+          <t>32,1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>32,8</t>
+          <t>33,1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>33,2</t>
+          <t>34,4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>38,1</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>41,9</t>
+          <t>41,6</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>34,3</t>
+          <t>32,2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>31,8</t>
+          <t>31,5</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>39,1</t>
+          <t>38,1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>31,7</t>
+          <t>31,4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>32,1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>32,4</t>
+          <t>32,3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>33,8</t>
+          <t>32,5</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>34,2</t>
+          <t>34,9</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>32,4</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>31,6</t>
+          <t>32,8</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>33,7</t>
+          <t>33,9</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>35,9</t>
+          <t>36,9</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>33,2</t>
+          <t>32,9</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>36,9</t>
+          <t>37,3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>32,7</t>
+          <t>32,6</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>29,1</t>
+          <t>29,2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>40,3</t>
+          <t>40,6</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>27,9</t>
+          <t>28,6</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>28,1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>32,9</t>
+          <t>32,8</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -446,17 +446,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>34,8</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>32,5</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -490,17 +490,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30,2</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -512,17 +512,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>38,5</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -534,17 +534,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>33,1</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -556,17 +556,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>31,1</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -578,17 +578,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>28,3</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>33,1</t>
+          <t>33,2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>34,4</t>
+          <t>33,9</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38,8</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>41,6</t>
+          <t>42,1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>31,5</t>
+          <t>31,4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>32,2</t>
+          <t>32,8</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>31,5</t>
+          <t>31,2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>38,1</t>
+          <t>37,8</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>31,4</t>
+          <t>30,9</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>32,1</t>
+          <t>31,4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>32,3</t>
+          <t>32,2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>32,5</t>
+          <t>32,9</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>34,9</t>
+          <t>34,2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32,7</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>32,8</t>
+          <t>32,6</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>33,9</t>
+          <t>32,6</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>36,9</t>
+          <t>37,2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>32,9</t>
+          <t>33,1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>37,3</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>32,6</t>
+          <t>31,6</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>29,2</t>
+          <t>29,3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>40,6</t>
+          <t>41,2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>28,6</t>
+          <t>28,1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>28,1</t>
+          <t>28,3</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>32,8</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -446,17 +446,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>33,5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -490,17 +490,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>29,8</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -512,17 +512,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>38,7</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -534,17 +534,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>32,6</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -556,17 +556,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>29,3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -578,17 +578,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>28,8</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>32,1</t>
+          <t>32,4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>34,2</t>
+          <t>34,5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>32,7</t>
+          <t>32,4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>32,6</t>
+          <t>32,5</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>32,6</t>
+          <t>32,5</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>37,2</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>33,1</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>36,7</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>31,6</t>
+          <t>32,3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>29,3</t>
+          <t>29,1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>41,2</t>
+          <t>41,6</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>28,1</t>
+          <t>28,4</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>28,3</t>
+          <t>28,1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32,9</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -444,11 +444,7 @@
           <t>ADANA</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>33,5</t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>25</t>
@@ -468,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>28,8</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -490,7 +486,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>29,8</t>
+          <t>29,7</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -512,7 +508,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>38,7</t>
+          <t>32,7</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -534,7 +530,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>32,6</t>
+          <t>30,2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -556,7 +552,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>29,3</t>
+          <t>28,3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -578,7 +574,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>28,8</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -600,7 +596,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>32,4</t>
+          <t>29,3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -622,7 +618,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>33,2</t>
+          <t>29,2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -644,7 +640,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>33,9</t>
+          <t>27,9</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -666,7 +662,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>38,8</t>
+          <t>31,4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -688,7 +684,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>42,1</t>
+          <t>37,4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -710,7 +706,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>31,4</t>
+          <t>26,7</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -732,7 +728,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>32,8</t>
+          <t>26,1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -754,7 +750,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>31,2</t>
+          <t>27,8</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -776,7 +772,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>37,8</t>
+          <t>37,1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -798,7 +794,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>30,9</t>
+          <t>29,8</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -820,7 +816,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>31,4</t>
+          <t>28,6</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -842,7 +838,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>32,2</t>
+          <t>32,4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -864,7 +860,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>32,9</t>
+          <t>30,7</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -886,7 +882,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>34,5</t>
+          <t>28,1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -908,7 +904,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>32,4</t>
+          <t>31,3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -930,7 +926,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>32,5</t>
+          <t>27,9</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -952,7 +948,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>32,5</t>
+          <t>30,2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -974,7 +970,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>29,8</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -996,7 +992,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>31,5</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1018,7 +1014,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>36,7</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1040,7 +1036,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>32,3</t>
+          <t>28,9</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1062,7 +1058,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>29,1</t>
+          <t>27,7</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1084,7 +1080,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>41,6</t>
+          <t>39,1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1106,7 +1102,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>28,4</t>
+          <t>27,4</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1128,7 +1124,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>28,1</t>
+          <t>27,2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1150,7 +1146,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>32,9</t>
+          <t>30,2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -444,15 +444,19 @@
           <t>ADANA</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>34,3</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -464,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>28,8</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -486,12 +490,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>29,7</t>
+          <t>30,1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -508,17 +512,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>32,7</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -530,17 +534,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>30,2</t>
+          <t>33,7</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -552,7 +556,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>28,3</t>
+          <t>31,2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -574,12 +578,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28,4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -596,17 +600,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>29,3</t>
+          <t>34,2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -618,7 +622,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>29,2</t>
+          <t>34,2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -628,7 +632,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -640,7 +644,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>27,9</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -662,7 +666,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>31,4</t>
+          <t>38,4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -684,12 +688,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>37,4</t>
+          <t>41,8</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -706,7 +710,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>26,7</t>
+          <t>32,2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -728,17 +732,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>26,1</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -750,12 +754,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>27,8</t>
+          <t>31,9</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -772,17 +776,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>37,1</t>
+          <t>37,8</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -794,7 +798,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>29,8</t>
+          <t>31,9</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -804,7 +808,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -816,7 +820,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>28,6</t>
+          <t>33,4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -826,7 +830,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -838,12 +842,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>32,4</t>
+          <t>34,8</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -860,12 +864,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>30,7</t>
+          <t>33,6</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -882,17 +886,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>28,1</t>
+          <t>33,4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -904,17 +908,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>31,3</t>
+          <t>34,4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -926,12 +930,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>27,9</t>
+          <t>34,1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -948,7 +952,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>30,2</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -970,12 +974,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>29,8</t>
+          <t>36,9</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -992,7 +996,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>31,5</t>
+          <t>32,3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,17 +1018,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>36,1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1040,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>28,9</t>
+          <t>32,3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1058,7 +1062,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>27,7</t>
+          <t>27,2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1080,17 +1084,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>39,1</t>
+          <t>41,7</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -1102,17 +1106,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>27,4</t>
+          <t>29,1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1128,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>27,2</t>
+          <t>28,8</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1150,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>30,2</t>
+          <t>33,5</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -446,17 +446,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>34,3</t>
+          <t>35,6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30,1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30,1</t>
+          <t>30,2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34,9</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -534,17 +534,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>33,7</t>
+          <t>31,8</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>31,2</t>
+          <t>29,7</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -578,12 +578,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>28,4</t>
+          <t>27,6</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>34,2</t>
+          <t>33,1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -622,12 +622,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>34,2</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>26,4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -666,17 +666,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>38,4</t>
+          <t>34,1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -688,17 +688,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>41,8</t>
+          <t>38,7</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -710,12 +710,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>32,2</t>
+          <t>29,6</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>26,2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -754,17 +754,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>31,9</t>
+          <t>28,7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -776,17 +776,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>37,8</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
     </row>
@@ -798,17 +798,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>31,9</t>
+          <t>30,4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -820,17 +820,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>33,4</t>
+          <t>31,5</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -842,17 +842,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>34,8</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>33,6</t>
+          <t>30,5</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>33,4</t>
+          <t>29,3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>34,4</t>
+          <t>32,9</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>34,1</t>
+          <t>30,6</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>30,6</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>36,9</t>
+          <t>32,4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>32,3</t>
+          <t>32,7</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>36,1</t>
+          <t>34,5</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>32,3</t>
+          <t>31,1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>27,2</t>
+          <t>28,6</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>41,7</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>29,1</t>
+          <t>28,1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>28,8</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1150,17 +1150,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>33,5</t>
+          <t>32,7</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -446,17 +446,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>35,6</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>30,1</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -490,17 +490,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30,2</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -512,17 +512,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>34,9</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -534,17 +534,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>31,8</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -556,17 +556,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>29,7</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -578,17 +578,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>27,6</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -600,17 +600,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>33,1</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>26,4</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -666,17 +666,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>34,1</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -688,17 +688,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>38,7</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -710,17 +710,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>29,6</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -732,17 +732,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>26,2</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -754,17 +754,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>28,7</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -776,17 +776,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -798,17 +798,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>30,4</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -820,17 +820,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>31,5</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -842,17 +842,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -864,17 +864,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>30,5</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -886,17 +886,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>29,3</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -908,17 +908,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>32,9</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>30,6</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>30,6</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -974,17 +974,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>32,4</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -996,17 +996,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>32,7</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -1018,17 +1018,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>34,5</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -1040,17 +1040,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>31,1</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -1062,17 +1062,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>28,6</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -1084,17 +1084,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -1106,17 +1106,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>28,1</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -1128,17 +1128,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -1150,17 +1150,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>32,7</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -446,17 +446,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>33,6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -490,17 +490,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>30,7</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -512,17 +512,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>37,8</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -534,17 +534,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -556,17 +556,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>30,9</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -578,17 +578,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>28,2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -600,17 +600,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>32,4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>34,8</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>29,7</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -666,17 +666,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -688,17 +688,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -710,17 +710,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>30,1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -732,17 +732,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>28,8</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -754,17 +754,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>31,4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -776,17 +776,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>38,2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -798,17 +798,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -820,17 +820,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>30,5</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -842,17 +842,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>34,7</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -864,17 +864,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>31,2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -886,17 +886,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>31,6</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -908,17 +908,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>33,8</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>32,4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>34,3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -974,17 +974,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>38,1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -996,17 +996,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>32,4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -1018,17 +1018,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -1040,17 +1040,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>30,2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -1062,17 +1062,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>28,4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -1084,17 +1084,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>39,2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -1106,17 +1106,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -1128,17 +1128,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>27,6</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -1150,17 +1150,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>33,9</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>35</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -446,17 +446,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>33,6</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -490,17 +490,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30,7</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -512,17 +512,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>37,8</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -534,17 +534,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -556,17 +556,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>30,9</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>28,2</t>
+          <t>25,3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>32,4</t>
+          <t>28,8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>34,8</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>29,7</t>
+          <t>25,1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>32,4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37,3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>30,1</t>
+          <t>27,9</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>28,8</t>
+          <t>23,3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>31,4</t>
+          <t>25,9</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>38,2</t>
+          <t>35,5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>30,8</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>30,5</t>
+          <t>27,8</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>34,7</t>
+          <t>30,5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>31,2</t>
+          <t>26,7</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>31,6</t>
+          <t>27,8</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>33,8</t>
+          <t>30,5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>32,4</t>
+          <t>26,2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>34,3</t>
+          <t>29,3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>38,1</t>
+          <t>29,2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>32,4</t>
+          <t>31,9</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>31,2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>30,2</t>
+          <t>27,3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>28,4</t>
+          <t>27,1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>39,2</t>
+          <t>32,1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>29,8</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>27,6</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>33,9</t>
+          <t>30,1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -578,17 +578,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25,3</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -600,17 +600,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>28,8</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>25,1</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -666,17 +666,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>32,4</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -688,17 +688,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>37,3</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>27,9</t>
+          <t>28,4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>23,3</t>
+          <t>24,5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>25,9</t>
+          <t>26,7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>35,5</t>
+          <t>35,6</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>30,8</t>
+          <t>30,4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>27,8</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>30,5</t>
+          <t>30,9</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>26,7</t>
+          <t>27,8</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>27,8</t>
+          <t>28,2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>30,5</t>
+          <t>31,1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>26,2</t>
+          <t>27,8</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>29,3</t>
+          <t>29,8</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>29,2</t>
+          <t>29,6</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>31,9</t>
+          <t>32,2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>31,2</t>
+          <t>32,2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>27,3</t>
+          <t>27,8</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>27,1</t>
+          <t>27,6</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>29,8</t>
+          <t>29,6</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28,1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>30,1</t>
+          <t>30,6</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -556,17 +556,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>26,1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -578,17 +578,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>25,9</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -600,17 +600,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>28,9</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>28,2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>25,6</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -666,17 +666,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>32,2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -688,17 +688,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>37,9</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>35,6</t>
+          <t>35,9</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>30,4</t>
+          <t>31,1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>27,9</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>30,9</t>
+          <t>31,7</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>27,8</t>
+          <t>28,3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>28,2</t>
+          <t>28,5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>31,1</t>
+          <t>30,9</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>27,8</t>
+          <t>27,9</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>29,8</t>
+          <t>29,9</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>29,6</t>
+          <t>29,5</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>32,2</t>
+          <t>32,4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>27,8</t>
+          <t>28,9</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>27,6</t>
+          <t>27,7</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>29,6</t>
+          <t>29,2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>28,1</t>
+          <t>27,9</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>30,6</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>30,4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -490,17 +490,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>30,6</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -512,17 +512,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -534,17 +534,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>31,7</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -556,17 +556,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26,1</t>
+          <t>28,7</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -578,17 +578,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25,9</t>
+          <t>28,6</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -600,17 +600,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>28,9</t>
+          <t>30,6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>28,2</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>25,6</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>32,2</t>
+          <t>36,3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
     </row>
@@ -688,17 +688,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>37,9</t>
+          <t>39,6</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>28,4</t>
+          <t>30,1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -732,17 +732,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>24,5</t>
+          <t>27,7</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -754,12 +754,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>26,7</t>
+          <t>30,5</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -776,17 +776,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>35,9</t>
+          <t>37,5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
     </row>
@@ -798,17 +798,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>31,1</t>
+          <t>31,8</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -820,17 +820,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>27,9</t>
+          <t>28,2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>31,7</t>
+          <t>31,2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>28,3</t>
+          <t>29,4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -886,17 +886,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>28,5</t>
+          <t>31,4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>30,9</t>
+          <t>32,9</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>27,9</t>
+          <t>30,8</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>29,9</t>
+          <t>32,4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>29,5</t>
+          <t>33,3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>32,2</t>
+          <t>32,9</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -1018,17 +1018,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>32,4</t>
+          <t>35,8</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -1040,12 +1040,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>28,9</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>27,7</t>
+          <t>28,3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1084,17 +1084,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>32,1</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>42</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>29,2</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1128,12 +1128,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>27,9</t>
+          <t>28,4</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1150,17 +1150,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>31,9</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -468,7 +468,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>30,4</t>
+          <t>29,5</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30,6</t>
+          <t>30,4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -512,7 +512,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>33,8</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>31,7</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -556,7 +556,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>28,7</t>
+          <t>30,7</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>28,6</t>
+          <t>28,2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>30,6</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33,2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30,1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>36,3</t>
+          <t>33,5</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>39,6</t>
+          <t>38,7</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>30,1</t>
+          <t>31,2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>27,7</t>
+          <t>26,7</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>30,5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>37,5</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>31,8</t>
+          <t>30,8</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>28,2</t>
+          <t>26,7</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>31,2</t>
+          <t>34,5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>29,4</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>31,4</t>
+          <t>31,2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>32,9</t>
+          <t>33,3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>30,8</t>
+          <t>31,4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>32,4</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>33,3</t>
+          <t>33,4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>32,9</t>
+          <t>33,2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>35,8</t>
+          <t>34,9</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32,3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27,1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>28,4</t>
+          <t>25,6</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>31,9</t>
+          <t>32,1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -468,7 +468,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>29,5</t>
+          <t>30,1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -478,7 +478,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -490,17 +490,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30,4</t>
+          <t>30,9</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>33,8</t>
+          <t>36,2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>30,8</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -556,7 +556,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>30,7</t>
+          <t>27,4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -578,17 +578,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>28,2</t>
+          <t>26,2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29,7</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>33,2</t>
+          <t>29,7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>30,1</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -666,12 +666,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>33,5</t>
+          <t>33,7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -688,17 +688,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>38,7</t>
+          <t>37,2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -710,17 +710,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>31,2</t>
+          <t>27,3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -732,17 +732,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>26,7</t>
+          <t>24,6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -754,17 +754,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>27,7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -776,17 +776,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>37,9</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>30,8</t>
+          <t>31,7</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>26,7</t>
+          <t>25,3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>34,5</t>
+          <t>35,1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -864,17 +864,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31,8</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>31,2</t>
+          <t>29,9</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -908,17 +908,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>33,3</t>
+          <t>29,8</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>31,4</t>
+          <t>30,5</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31,9</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -979,7 +979,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>34,9</t>
+          <t>35,6</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>32,3</t>
+          <t>30,4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>28,3</t>
+          <t>29,4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1084,17 +1084,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>27,1</t>
+          <t>28,3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>25,6</t>
+          <t>24,3</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1150,17 +1150,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>32,1</t>
+          <t>31,2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -446,17 +446,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>35,8</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -468,7 +468,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>30,1</t>
+          <t>29,9</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -478,7 +478,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30,9</t>
+          <t>39,1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -512,12 +512,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>36,2</t>
+          <t>33,9</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>30,8</t>
+          <t>29,4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -578,12 +578,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>26,2</t>
+          <t>25,5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -605,12 +605,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>29,7</t>
+          <t>28,1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -644,12 +644,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25,7</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -666,17 +666,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>33,7</t>
+          <t>31,4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>37,2</t>
+          <t>36,4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>27,3</t>
+          <t>26,8</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -732,17 +732,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>24,6</t>
+          <t>23,2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>27,7</t>
+          <t>27,4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>37,9</t>
+          <t>36,5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>31,7</t>
+          <t>31,8</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -820,12 +820,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>25,3</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>35,1</t>
+          <t>32,2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>31,8</t>
+          <t>25,4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -886,17 +886,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>29,9</t>
+          <t>27,2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -908,17 +908,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>29,8</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -930,12 +930,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>30,5</t>
+          <t>30,2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -952,17 +952,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>31,9</t>
+          <t>25,2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -974,17 +974,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>33,4</t>
+          <t>30,1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>39</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>33,2</t>
+          <t>32,5</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1018,17 +1018,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>35,6</t>
+          <t>32,6</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>30,4</t>
+          <t>28,6</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>29,4</t>
+          <t>26,1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1084,17 +1084,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34,9</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
     </row>
@@ -1106,17 +1106,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>28,3</t>
+          <t>29,4</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>24,3</t>
+          <t>27,5</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1150,17 +1150,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>31,2</t>
+          <t>27,7</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>35</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -446,17 +446,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>35,8</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>29,9</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -490,17 +490,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>39,1</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -510,21 +510,9 @@
           <t>AYDIN</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>33,9</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -534,12 +522,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>29,4</t>
+          <t>32,5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -556,17 +544,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>27,4</t>
+          <t>29,6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -578,7 +566,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25,5</t>
+          <t>28,5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -588,7 +576,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -600,17 +588,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>29,7</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -622,12 +610,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>28,1</t>
+          <t>32,1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -644,17 +632,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>25,7</t>
+          <t>30,1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -666,17 +654,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>31,4</t>
+          <t>35,9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -688,17 +676,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>36,4</t>
+          <t>36,5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
     </row>
@@ -710,12 +698,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>26,8</t>
+          <t>30,2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -732,17 +720,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>23,2</t>
+          <t>24,9</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -754,17 +742,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>27,4</t>
+          <t>30,2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -776,12 +764,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>36,5</t>
+          <t>36,6</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -798,17 +786,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>31,8</t>
+          <t>32,8</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -820,7 +808,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30,1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -830,7 +818,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -842,7 +830,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>32,2</t>
+          <t>36,1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -852,7 +840,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -864,17 +852,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>25,4</t>
+          <t>28,6</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -886,7 +874,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>27,2</t>
+          <t>30,1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -908,7 +896,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31,2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -918,7 +906,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -930,7 +918,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>30,2</t>
+          <t>32,2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -952,7 +940,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>25,2</t>
+          <t>28,5</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -962,7 +950,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -974,7 +962,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>30,1</t>
+          <t>34,7</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -984,7 +972,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -996,17 +984,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>32,5</t>
+          <t>34,1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -1018,17 +1006,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>32,6</t>
+          <t>36,8</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1028,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>28,6</t>
+          <t>32,2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1050,7 +1038,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -1062,17 +1050,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>26,1</t>
+          <t>28,5</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -1084,17 +1072,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>34,9</t>
+          <t>37,5</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -1106,17 +1094,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>29,4</t>
+          <t>31,1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -1128,12 +1116,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>27,5</t>
+          <t>28,4</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1150,7 +1138,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>27,7</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -446,17 +446,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>36,6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>29,4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -490,17 +490,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>39,7</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>39</t>
         </is>
       </c>
     </row>
@@ -510,9 +510,21 @@
           <t>AYDIN</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>36,2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -522,7 +534,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>32,5</t>
+          <t>30,3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -544,7 +556,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>29,6</t>
+          <t>28,8</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -566,7 +578,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>28,5</t>
+          <t>26,4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -588,7 +600,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30,1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -610,7 +622,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>32,1</t>
+          <t>28,8</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -632,7 +644,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>30,1</t>
+          <t>27,8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -654,7 +666,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>35,9</t>
+          <t>34,3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -676,7 +688,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>36,5</t>
+          <t>35,5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -698,7 +710,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>30,2</t>
+          <t>27,8</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -720,7 +732,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>24,9</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -742,7 +754,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>30,2</t>
+          <t>28,7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -764,7 +776,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>36,6</t>
+          <t>35,5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -786,7 +798,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>32,8</t>
+          <t>31,3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -808,7 +820,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>30,1</t>
+          <t>28,1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -830,7 +842,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>36,1</t>
+          <t>33,6</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -852,7 +864,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>28,6</t>
+          <t>26,1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -874,7 +886,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>30,1</t>
+          <t>28,2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -896,7 +908,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>31,2</t>
+          <t>29,6</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -918,7 +930,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>32,2</t>
+          <t>29,9</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -940,7 +952,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>28,5</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -962,7 +974,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>34,7</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -984,7 +996,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>34,1</t>
+          <t>32,4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1006,7 +1018,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>36,8</t>
+          <t>34,9</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1028,7 +1040,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>32,2</t>
+          <t>29,4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1050,7 +1062,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>28,5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1072,7 +1084,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>37,5</t>
+          <t>34,6</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1094,7 +1106,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>31,1</t>
+          <t>27,7</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1116,7 +1128,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>28,4</t>
+          <t>24,2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1138,7 +1150,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30,8</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -446,17 +446,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>36,6</t>
+          <t>37,3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -468,7 +468,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>29,4</t>
+          <t>31,5</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -478,7 +478,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -490,17 +490,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>39,7</t>
+          <t>34,9</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>36,2</t>
+          <t>38,4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -534,12 +534,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>30,3</t>
+          <t>31,9</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -556,12 +556,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>28,8</t>
+          <t>31,2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -578,12 +578,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>26,4</t>
+          <t>30,5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -600,17 +600,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>30,1</t>
+          <t>32,1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>28,8</t>
+          <t>31,1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>27,8</t>
+          <t>29,4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -666,17 +666,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>34,3</t>
+          <t>37,8</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -688,12 +688,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>35,5</t>
+          <t>38,8</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -710,12 +710,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>27,8</t>
+          <t>30,2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -732,17 +732,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25,6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>28,7</t>
+          <t>30,6</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>35,5</t>
+          <t>36,2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>31,3</t>
+          <t>32,5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -820,17 +820,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>28,1</t>
+          <t>29,7</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>33,6</t>
+          <t>36,1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>26,1</t>
+          <t>29,3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -886,17 +886,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>28,2</t>
+          <t>29,7</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -908,17 +908,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>29,6</t>
+          <t>31,6</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>29,9</t>
+          <t>31,6</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>34,4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -996,17 +996,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>32,4</t>
+          <t>33,6</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -1018,17 +1018,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>34,9</t>
+          <t>35,2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>29,4</t>
+          <t>31,2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29,8</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>34,6</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1106,17 +1106,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>27,7</t>
+          <t>28,8</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -1128,17 +1128,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>24,2</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -1150,17 +1150,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>30,8</t>
+          <t>32,9</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -446,7 +446,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>37,3</t>
+          <t>37,1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -456,7 +456,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>31,5</t>
+          <t>31,8</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>34,9</t>
+          <t>36,4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
     </row>
@@ -512,17 +512,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>38,4</t>
+          <t>36,2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>31,9</t>
+          <t>32,9</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -556,17 +556,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>31,2</t>
+          <t>31,5</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -578,17 +578,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>30,5</t>
+          <t>30,4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>32,1</t>
+          <t>33,5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>31,1</t>
+          <t>33,4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>29,4</t>
+          <t>29,9</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -666,17 +666,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>37,8</t>
+          <t>37,9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -688,12 +688,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>38,8</t>
+          <t>39,4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>30,2</t>
+          <t>29,7</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>25,6</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -754,17 +754,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>30,6</t>
+          <t>31,8</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>36,2</t>
+          <t>37,1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -798,17 +798,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>32,5</t>
+          <t>33,3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -820,17 +820,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>29,7</t>
+          <t>31,7</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -842,17 +842,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>36,1</t>
+          <t>34,7</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>29,3</t>
+          <t>30,7</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -886,17 +886,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>29,7</t>
+          <t>30,8</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -908,17 +908,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>31,6</t>
+          <t>33,3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30,7</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -974,17 +974,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>34,4</t>
+          <t>34,7</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>33,6</t>
+          <t>33,3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1018,17 +1018,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>35,2</t>
+          <t>37,1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>31,2</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -1062,17 +1062,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>29,8</t>
+          <t>29,2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38,3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -1106,17 +1106,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>28,8</t>
+          <t>28,6</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28,6</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -1150,17 +1150,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>32,9</t>
+          <t>32,3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>31</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -446,12 +446,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>37,1</t>
+          <t>38,9</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>31,8</t>
+          <t>30,5</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -490,17 +490,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>36,4</t>
+          <t>37,3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -512,17 +512,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>36,2</t>
+          <t>38,6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -534,17 +534,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>32,9</t>
+          <t>32,6</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -556,17 +556,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>31,5</t>
+          <t>30,7</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -578,17 +578,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>30,4</t>
+          <t>29,4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -600,17 +600,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>33,5</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>33,4</t>
+          <t>32,2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>29,9</t>
+          <t>27,5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -666,17 +666,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>37,9</t>
+          <t>36,5</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -688,17 +688,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>39,4</t>
+          <t>39,3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -710,17 +710,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>29,7</t>
+          <t>30,6</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>26,3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -754,17 +754,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>31,8</t>
+          <t>30,7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -776,17 +776,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>37,1</t>
+          <t>38,4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -798,17 +798,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>33,3</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>31,7</t>
+          <t>30,1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -842,17 +842,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>34,7</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -864,17 +864,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>30,7</t>
+          <t>30,4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -886,17 +886,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>30,8</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -908,17 +908,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>33,3</t>
+          <t>29,3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -930,12 +930,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>31,6</t>
+          <t>32,6</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -952,17 +952,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>30,7</t>
+          <t>28,2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -974,17 +974,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>34,7</t>
+          <t>35,3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>33,3</t>
+          <t>33,6</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -1018,17 +1018,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>37,1</t>
+          <t>35,2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -1040,12 +1040,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31,6</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>29,2</t>
+          <t>29,9</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1084,17 +1084,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>38,3</t>
+          <t>37,2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -1106,17 +1106,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>28,6</t>
+          <t>29,9</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>28,6</t>
+          <t>28,4</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -1150,17 +1150,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>32,3</t>
+          <t>30,7</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -446,17 +446,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>38,9</t>
+          <t>37,2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>30,5</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -490,17 +490,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>37,3</t>
+          <t>40,3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -512,17 +512,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>38,6</t>
+          <t>36,5</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -534,12 +534,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>32,6</t>
+          <t>29,8</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -556,17 +556,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>30,7</t>
+          <t>25,4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -578,12 +578,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>29,4</t>
+          <t>24,3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29,3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>32,2</t>
+          <t>28,9</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>27,5</t>
+          <t>25,3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -666,17 +666,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>36,5</t>
+          <t>34,3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -688,17 +688,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>39,3</t>
+          <t>38,9</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -710,12 +710,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>30,6</t>
+          <t>27,1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>26,3</t>
+          <t>22,3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -754,17 +754,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>30,7</t>
+          <t>26,7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>38,4</t>
+          <t>36,4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -798,17 +798,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>31,8</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>32</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>31</t>
         </is>
       </c>
     </row>
@@ -820,17 +820,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>30,1</t>
+          <t>27,6</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34,6</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>30,4</t>
+          <t>27,8</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -886,12 +886,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26,4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>29,3</t>
+          <t>26,4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>32,6</t>
+          <t>29,5</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>28,2</t>
+          <t>27,7</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -974,17 +974,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>35,3</t>
+          <t>32,8</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>33,6</t>
+          <t>33,4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1018,17 +1018,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>35,2</t>
+          <t>33,5</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>31,6</t>
+          <t>28,4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1062,17 +1062,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>29,9</t>
+          <t>27,6</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>37,2</t>
+          <t>36,9</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -1106,17 +1106,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>29,9</t>
+          <t>27,5</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -1128,17 +1128,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>28,4</t>
+          <t>26,1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -1150,17 +1150,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>30,7</t>
+          <t>29,9</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -446,7 +446,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>37,2</t>
+          <t>33,4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -468,7 +468,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>23,9</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>40,3</t>
+          <t>36,9</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -512,7 +512,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>36,5</t>
+          <t>30,7</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>29,8</t>
+          <t>26,6</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -556,7 +556,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25,4</t>
+          <t>22,3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>24,3</t>
+          <t>21,6</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>29,3</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>28,9</t>
+          <t>24,8</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>25,3</t>
+          <t>20,4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>34,3</t>
+          <t>27,8</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>38,9</t>
+          <t>35,2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>27,1</t>
+          <t>24,2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>22,3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>26,7</t>
+          <t>22,6</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>36,4</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>31,8</t>
+          <t>31,2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>27,6</t>
+          <t>26,8</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>34,6</t>
+          <t>29,4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>27,8</t>
+          <t>21,6</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>26,4</t>
+          <t>20,8</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>26,4</t>
+          <t>24,4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>29,5</t>
+          <t>26,2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>27,7</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>32,8</t>
+          <t>27,1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>33,4</t>
+          <t>32,2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>33,5</t>
+          <t>30,3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>28,4</t>
+          <t>24,5</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>27,6</t>
+          <t>26,5</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>36,9</t>
+          <t>31,1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>27,5</t>
+          <t>25,3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>26,1</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>29,9</t>
+          <t>25,3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -446,12 +446,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>33,4</t>
+          <t>32,7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>23,9</t>
+          <t>24,5</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -490,17 +490,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>36,9</t>
+          <t>30,2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30,7</t>
+          <t>29,4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -522,7 +522,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>26,6</t>
+          <t>25,8</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -556,17 +556,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>22,3</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -578,17 +578,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>21,6</t>
+          <t>22,1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -600,17 +600,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25,9</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -627,12 +627,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20,4</t>
+          <t>19,2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -666,17 +666,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>27,8</t>
+          <t>27,7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -688,17 +688,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>35,2</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -710,12 +710,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>24,2</t>
+          <t>23,4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21,6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -754,17 +754,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>22,6</t>
+          <t>23,3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -776,17 +776,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>30,7</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -798,17 +798,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>31,2</t>
+          <t>30,3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>26,8</t>
+          <t>26,3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -842,17 +842,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>29,4</t>
+          <t>29,3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -864,17 +864,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>21,6</t>
+          <t>23,8</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -886,12 +886,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20,8</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -908,17 +908,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>24,4</t>
+          <t>24,1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -930,12 +930,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>26,2</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24,6</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -974,17 +974,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>27,1</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -996,17 +996,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>32,2</t>
+          <t>33,2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>30,3</t>
+          <t>24,6</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1040,17 +1040,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>24,5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>26,5</t>
+          <t>24,4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1084,17 +1084,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>31,1</t>
+          <t>31,6</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>25,3</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1128,17 +1128,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -1150,17 +1150,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>25,3</t>
+          <t>23,5</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -446,17 +446,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>32,7</t>
+          <t>33,4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>24,5</t>
+          <t>27,9</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30,2</t>
+          <t>29,7</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -512,17 +512,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>29,4</t>
+          <t>29,8</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -534,17 +534,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,8</t>
+          <t>28,6</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>23,6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -578,17 +578,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>22,1</t>
+          <t>24,3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -600,17 +600,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>25,9</t>
+          <t>28,1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>24,8</t>
+          <t>27,6</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>19,2</t>
+          <t>25,1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -666,17 +666,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>27,7</t>
+          <t>29,5</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -688,17 +688,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>34,1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>23,4</t>
+          <t>26,5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>21,6</t>
+          <t>23,5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>23,3</t>
+          <t>24,8</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -776,17 +776,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>30,7</t>
+          <t>31,4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -798,12 +798,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>30,3</t>
+          <t>30,9</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -820,17 +820,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>26,3</t>
+          <t>26,5</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -842,17 +842,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>29,3</t>
+          <t>28,5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -864,17 +864,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>23,8</t>
+          <t>24,8</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -886,17 +886,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24,3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>24,1</t>
+          <t>25,8</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25,9</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>24,6</t>
+          <t>27,1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -974,17 +974,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27,6</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>33,2</t>
+          <t>31,8</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>24,6</t>
+          <t>28,4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27,7</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>24,4</t>
+          <t>28,1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1084,17 +1084,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>31,6</t>
+          <t>32,6</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25,8</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26,7</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>23,5</t>
+          <t>26,1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -446,12 +446,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>33,4</t>
+          <t>32,9</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>27,9</t>
+          <t>25,4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -490,12 +490,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>29,7</t>
+          <t>28,5</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -512,7 +512,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>29,8</t>
+          <t>30,1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -522,7 +522,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -534,17 +534,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>28,6</t>
+          <t>26,8</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -556,17 +556,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>23,6</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -578,17 +578,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>24,3</t>
+          <t>23,2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -600,17 +600,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>28,1</t>
+          <t>27,3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>27,6</t>
+          <t>26,5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>25,1</t>
+          <t>24,3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>29,5</t>
+          <t>29,6</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -688,17 +688,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>34,1</t>
+          <t>34,2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>26,5</t>
+          <t>25,8</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -732,17 +732,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>23,5</t>
+          <t>22,1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -754,12 +754,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>24,8</t>
+          <t>25,7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -776,17 +776,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>31,4</t>
+          <t>28,7</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -820,17 +820,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>26,5</t>
+          <t>23,1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>28,5</t>
+          <t>28,6</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -864,17 +864,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>24,8</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -886,12 +886,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>24,3</t>
+          <t>26,3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -908,17 +908,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>25,8</t>
+          <t>26,5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -930,12 +930,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>25,9</t>
+          <t>26,6</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -952,17 +952,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>27,1</t>
+          <t>26,6</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -996,17 +996,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>31,8</t>
+          <t>31,5</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>28,4</t>
+          <t>29,4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1040,12 +1040,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>27,7</t>
+          <t>27,8</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>28,1</t>
+          <t>27,4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -1084,17 +1084,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>32,6</t>
+          <t>30,3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -1106,17 +1106,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>25,8</t>
+          <t>24,5</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -1128,17 +1128,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>26,7</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>26,1</t>
+          <t>25,1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -446,7 +446,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>32,9</t>
+          <t>35,4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -456,7 +456,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>39</t>
         </is>
       </c>
     </row>
@@ -468,7 +468,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>25,4</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -478,7 +478,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -490,17 +490,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>28,5</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -512,17 +512,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30,1</t>
+          <t>33,1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -534,17 +534,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>26,8</t>
+          <t>31,4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -556,17 +556,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28,1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -578,17 +578,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>23,2</t>
+          <t>25,6</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>27,3</t>
+          <t>29,3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -622,12 +622,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>26,5</t>
+          <t>29,6</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -644,12 +644,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>24,3</t>
+          <t>26,3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -666,17 +666,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>29,6</t>
+          <t>32,1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>39</t>
         </is>
       </c>
     </row>
@@ -688,17 +688,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>34,2</t>
+          <t>34,3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -710,17 +710,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>25,8</t>
+          <t>28,7</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -732,17 +732,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>22,1</t>
+          <t>20,6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -754,17 +754,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>25,7</t>
+          <t>27,7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -776,17 +776,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>28,7</t>
+          <t>34,7</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -798,17 +798,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>30,9</t>
+          <t>31,3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>23,1</t>
+          <t>28,5</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -842,12 +842,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>28,6</t>
+          <t>33,9</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -864,12 +864,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27,9</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -886,17 +886,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>26,3</t>
+          <t>27,6</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -908,17 +908,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>26,5</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>26,6</t>
+          <t>29,9</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -952,12 +952,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>26,6</t>
+          <t>28,3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>27,6</t>
+          <t>30,5</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>39</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>31,5</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -1018,17 +1018,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>29,4</t>
+          <t>33,1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>27,8</t>
+          <t>29,8</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>27,4</t>
+          <t>28,5</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -1084,17 +1084,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>30,3</t>
+          <t>36,1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>24,5</t>
+          <t>25,9</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -1128,17 +1128,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23,5</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -1150,17 +1150,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>25,1</t>
+          <t>29,9</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>34</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -446,7 +446,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>35,4</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -456,7 +456,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>29,6</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>34,5</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>33,1</t>
+          <t>34,2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -522,7 +522,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -534,12 +534,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>31,4</t>
+          <t>32,3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -556,17 +556,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>28,1</t>
+          <t>31,4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25,6</t>
+          <t>30,5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -600,17 +600,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>29,3</t>
+          <t>30,1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>29,6</t>
+          <t>27,7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>26,3</t>
+          <t>28,3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -666,12 +666,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>32,1</t>
+          <t>34,7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -688,17 +688,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>34,3</t>
+          <t>37,1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -710,17 +710,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>28,7</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -732,17 +732,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20,6</t>
+          <t>23,1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -754,17 +754,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>27,7</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -776,17 +776,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>34,7</t>
+          <t>35,7</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>31,3</t>
+          <t>33,6</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>28,5</t>
+          <t>29,2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>33,9</t>
+          <t>32,6</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -864,17 +864,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>27,9</t>
+          <t>26,5</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>27,6</t>
+          <t>28,5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31,3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -930,12 +930,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>29,9</t>
+          <t>31,4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -952,17 +952,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>28,3</t>
+          <t>29,2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>30,5</t>
+          <t>31,9</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>35,1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>33,1</t>
+          <t>35,8</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -1040,17 +1040,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>29,8</t>
+          <t>30,2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -1062,17 +1062,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>28,5</t>
+          <t>27,2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -1084,17 +1084,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>36,1</t>
+          <t>37,1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>25,9</t>
+          <t>26,1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>23,5</t>
+          <t>26,5</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>29,9</t>
+          <t>31,9</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -444,11 +444,7 @@
           <t>ADANA</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>24</t>
@@ -468,17 +464,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>29,6</t>
+          <t>28,7</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -490,7 +486,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>34,5</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -500,7 +496,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -512,12 +508,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>34,2</t>
+          <t>31,1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -534,12 +530,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>32,3</t>
+          <t>27,1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -556,17 +552,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>31,4</t>
+          <t>28,8</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -578,7 +574,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>30,5</t>
+          <t>27,4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -588,7 +584,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -600,17 +596,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>30,1</t>
+          <t>27,1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -622,17 +618,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>27,7</t>
+          <t>27,5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -644,17 +640,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>28,3</t>
+          <t>25,1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -666,7 +662,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>34,7</t>
+          <t>33,4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -688,17 +684,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>37,1</t>
+          <t>37,2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>42</t>
         </is>
       </c>
     </row>
@@ -710,17 +706,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25,9</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -732,17 +728,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>23,1</t>
+          <t>22,8</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -754,7 +750,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28,6</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -764,7 +760,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -776,17 +772,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>35,7</t>
+          <t>36,9</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -798,7 +794,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>33,6</t>
+          <t>30,6</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -808,7 +804,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -820,17 +816,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>29,2</t>
+          <t>24,9</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -842,17 +838,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>32,6</t>
+          <t>30,2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -864,17 +860,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>26,5</t>
+          <t>28,5</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -884,19 +880,15 @@
           <t>KIRIKKALE</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>28,5</t>
-        </is>
-      </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -908,17 +900,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>31,3</t>
+          <t>26,8</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -930,12 +922,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>31,4</t>
+          <t>27,2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -952,17 +944,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>29,2</t>
+          <t>29,1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -974,7 +966,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>31,9</t>
+          <t>30,1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -984,7 +976,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
     </row>
@@ -996,7 +988,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>35,1</t>
+          <t>31,5</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1018,7 +1010,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>35,8</t>
+          <t>31,7</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1028,7 +1020,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>39</t>
         </is>
       </c>
     </row>
@@ -1040,17 +1032,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>30,2</t>
+          <t>25,2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -1062,17 +1054,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>27,2</t>
+          <t>26,5</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -1084,17 +1076,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>37,1</t>
+          <t>37,9</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1098,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>26,1</t>
+          <t>25,9</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1128,17 +1120,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>26,5</t>
+          <t>26,4</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1142,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>31,9</t>
+          <t>29,3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1160,7 +1152,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -447,7 +447,7 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -464,17 +464,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>28,7</t>
+          <t>29,3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -486,17 +486,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30,1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -508,17 +508,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>31,1</t>
+          <t>31,6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>42</t>
         </is>
       </c>
     </row>
@@ -530,12 +530,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>27,1</t>
+          <t>30,1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -552,17 +552,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>28,8</t>
+          <t>26,6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -574,17 +574,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>27,4</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -596,17 +596,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>27,1</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -618,17 +618,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>27,5</t>
+          <t>30,7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -640,17 +640,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>25,1</t>
+          <t>28,9</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -662,17 +662,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>33,4</t>
+          <t>32,8</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -684,17 +684,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>37,2</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -706,12 +706,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>25,9</t>
+          <t>27,1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -728,17 +728,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>22,8</t>
+          <t>27,3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -750,17 +750,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>28,6</t>
+          <t>29,3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>36,9</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>39</t>
         </is>
       </c>
     </row>
@@ -794,7 +794,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>30,6</t>
+          <t>30,9</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -816,12 +816,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>24,9</t>
+          <t>25,2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -838,17 +838,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>30,2</t>
+          <t>30,8</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -860,17 +860,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>28,5</t>
+          <t>30,6</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -900,17 +900,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>26,8</t>
+          <t>32,1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -944,17 +944,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>29,1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -966,12 +966,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>30,1</t>
+          <t>33,3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>31,5</t>
+          <t>31,8</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>31,7</t>
+          <t>30,6</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1032,17 +1032,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>25,2</t>
+          <t>27,9</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>26,5</t>
+          <t>28,4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>37,9</t>
+          <t>35,1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1098,17 +1098,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>25,9</t>
+          <t>25,6</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -1120,17 +1120,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>26,4</t>
+          <t>27,8</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>29,3</t>
+          <t>30,5</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -447,7 +447,7 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>29,3</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -474,7 +474,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -486,17 +486,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30,1</t>
+          <t>31,9</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -508,17 +508,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>31,6</t>
+          <t>37,1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -530,17 +530,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>30,1</t>
+          <t>32,1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26,6</t>
+          <t>30,8</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -574,12 +574,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29,3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>33,7</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>30,7</t>
+          <t>29,4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>28,9</t>
+          <t>30,4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -662,7 +662,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>32,8</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -684,17 +684,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>38</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>41</t>
         </is>
       </c>
     </row>
@@ -706,17 +706,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>27,1</t>
+          <t>29,1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -728,17 +728,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>27,3</t>
+          <t>30,2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -750,12 +750,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>29,3</t>
+          <t>29,9</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -772,17 +772,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>36,7</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>37</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>39</t>
         </is>
       </c>
     </row>
@@ -794,12 +794,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>30,9</t>
+          <t>31,5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -816,17 +816,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>25,2</t>
+          <t>30,4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -838,17 +838,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>30,8</t>
+          <t>35,5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -860,17 +860,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>30,6</t>
+          <t>30,2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -880,15 +880,19 @@
           <t>KIRIKKALE</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -905,7 +909,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -922,12 +926,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>27,2</t>
+          <t>31,5</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -944,17 +948,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>30,6</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -966,7 +970,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>33,3</t>
+          <t>34,4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -976,7 +980,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -988,17 +992,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>31,8</t>
+          <t>32,8</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1014,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>30,6</t>
+          <t>37,9</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1032,17 +1036,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>27,9</t>
+          <t>30,9</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -1054,17 +1058,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>28,4</t>
+          <t>27,3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1080,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>35,1</t>
+          <t>32,8</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1086,7 +1090,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1102,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>25,6</t>
+          <t>28,2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1120,17 +1124,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>27,8</t>
+          <t>27,7</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1146,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>30,5</t>
+          <t>33,3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29,3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -474,7 +474,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -486,17 +486,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31,9</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -508,17 +508,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>37,1</t>
+          <t>35,6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -530,17 +530,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>32,1</t>
+          <t>31,2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>30,8</t>
+          <t>30,4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>29,3</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -584,7 +584,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -596,17 +596,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>33,7</t>
+          <t>29,7</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -618,17 +618,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>29,4</t>
+          <t>28,7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -640,17 +640,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>30,4</t>
+          <t>26,2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -662,7 +662,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34,7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
     </row>
@@ -684,12 +684,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37,8</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -706,17 +706,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>29,1</t>
+          <t>30,1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>30,2</t>
+          <t>27,3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -750,12 +750,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>29,9</t>
+          <t>29,8</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>36,7</t>
+          <t>34,1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>31,5</t>
+          <t>31,2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -816,17 +816,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>30,4</t>
+          <t>27,8</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -838,17 +838,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>35,5</t>
+          <t>34,6</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -860,17 +860,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>30,2</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>27,3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>32,1</t>
+          <t>31,5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -926,12 +926,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>31,5</t>
+          <t>26,5</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>30,6</t>
+          <t>28,3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>34,4</t>
+          <t>31,9</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>32,8</t>
+          <t>33,7</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>37,9</t>
+          <t>35,9</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>30,9</t>
+          <t>31,2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1056,19 +1056,15 @@
           <t>SAMSUN</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>27,3</t>
-        </is>
-      </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -1080,17 +1076,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>32,8</t>
+          <t>32,7</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
     </row>
@@ -1102,17 +1098,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>28,2</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -1124,7 +1120,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>27,7</t>
+          <t>26,7</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1146,17 +1142,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>33,3</t>
+          <t>32,6</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -447,7 +447,7 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -464,17 +464,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>29,3</t>
+          <t>28,7</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -486,17 +486,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31,8</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>35,6</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -530,12 +530,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>31,2</t>
+          <t>31,3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>30,4</t>
+          <t>30,8</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -574,17 +574,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>30,3</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>29</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>33</t>
         </is>
       </c>
     </row>
@@ -596,7 +596,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>29,7</t>
+          <t>29,5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -618,17 +618,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>28,7</t>
+          <t>29,6</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -640,17 +640,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>26,2</t>
+          <t>26,3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -662,12 +662,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>34,7</t>
+          <t>33,7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -684,12 +684,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>37,8</t>
+          <t>36,9</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -706,17 +706,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>30,1</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>27,3</t>
+          <t>25,9</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -750,17 +750,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>29,8</t>
+          <t>30,2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>34,1</t>
+          <t>34,7</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -794,12 +794,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>31,2</t>
+          <t>30,9</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>27,8</t>
+          <t>26,5</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -838,17 +838,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>34,6</t>
+          <t>33,6</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -860,17 +860,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25,7</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>27,3</t>
+          <t>28,4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -904,17 +904,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>31,5</t>
+          <t>31,1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -926,17 +926,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>26,5</t>
+          <t>29,6</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>28,3</t>
+          <t>29,6</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>31,9</t>
+          <t>32,2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -992,17 +992,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>33,7</t>
+          <t>32,8</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -1014,17 +1014,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>35,9</t>
+          <t>33,2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -1036,17 +1036,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>31,2</t>
+          <t>30,5</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -1056,15 +1056,19 @@
           <t>SAMSUN</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>28,1</t>
+        </is>
+      </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1080,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>32,7</t>
+          <t>34,5</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1098,7 +1102,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1120,12 +1124,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>26,7</t>
+          <t>27,7</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1142,12 +1146,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>32,6</t>
+          <t>30,2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -444,15 +444,19 @@
           <t>ADANA</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>HATA</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -464,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>28,7</t>
+          <t>25,8</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -486,7 +490,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31,8</t>
+          <t>28,3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -496,7 +500,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -508,17 +512,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33,8</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -530,17 +534,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>31,3</t>
+          <t>27,1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -552,17 +556,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>30,8</t>
+          <t>22,4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -574,17 +578,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>30,3</t>
+          <t>20,8</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -596,17 +600,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>29,5</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -618,17 +622,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>29,6</t>
+          <t>27,5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -640,17 +644,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>26,3</t>
+          <t>21,7</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -662,17 +666,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>33,7</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -684,17 +688,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>36,9</t>
+          <t>31,5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -706,17 +710,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>23,3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -728,17 +732,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>25,9</t>
+          <t>18,2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -750,17 +754,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>30,2</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -772,17 +776,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>34,7</t>
+          <t>28,8</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -794,17 +798,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>30,9</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -816,17 +820,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>26,5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -838,17 +842,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>33,6</t>
+          <t>31,6</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -860,17 +864,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>25,7</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -882,17 +886,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>28,4</t>
+          <t>27,3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -904,17 +908,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>31,1</t>
+          <t>24,8</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -926,17 +930,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>29,6</t>
+          <t>24,7</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -948,17 +952,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>29,6</t>
+          <t>28,4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -970,17 +974,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>32,2</t>
+          <t>30,6</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -992,12 +996,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>32,8</t>
+          <t>30,5</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1014,17 +1018,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>33,2</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -1036,17 +1040,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>30,5</t>
+          <t>24,3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -1058,17 +1062,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>28,1</t>
+          <t>24,8</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -1080,17 +1084,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>34,5</t>
+          <t>32,2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1106,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>26,3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1124,17 +1128,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>27,7</t>
+          <t>25,4</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -1146,17 +1150,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>30,2</t>
+          <t>25,1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>27</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>25,8</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -490,17 +490,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>28,3</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -512,17 +512,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>33,8</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -534,17 +534,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>27,1</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -556,17 +556,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>22,4</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -578,17 +578,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20,8</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -600,17 +600,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>27,5</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>21,7</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -666,12 +666,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>26,4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>31,5</t>
+          <t>28,1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>23,3</t>
+          <t>18,2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>18,2</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -754,17 +754,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>16,4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>28,8</t>
+          <t>24,1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -798,17 +798,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26,9</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -820,17 +820,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -842,17 +842,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>31,6</t>
+          <t>26,8</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -864,17 +864,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>17,2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>24</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
     </row>
@@ -886,12 +886,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>27,3</t>
+          <t>18,3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -908,17 +908,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>24,8</t>
+          <t>20,8</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>24,7</t>
+          <t>20,8</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>28,4</t>
+          <t>20,2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -974,17 +974,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>30,6</t>
+          <t>25,3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -996,17 +996,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>30,5</t>
+          <t>28,2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25,1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -1040,17 +1040,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>24,3</t>
+          <t>20,8</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -1062,17 +1062,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>24,8</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>32,2</t>
+          <t>29,9</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>26,3</t>
+          <t>21,4</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>25,4</t>
+          <t>23,9</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1150,17 +1150,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>25,1</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -444,19 +444,15 @@
           <t>ADANA</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>HATA</t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -468,17 +464,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -490,17 +486,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>35,5</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -512,17 +508,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>34,1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -534,17 +530,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>27,5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -556,17 +552,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>22,8</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -578,17 +574,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>18,6</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -600,17 +596,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>26,6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -622,17 +618,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>29,9</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -644,17 +640,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>23,1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -666,17 +662,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>26,4</t>
+          <t>30,1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -688,17 +684,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>28,1</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -710,7 +706,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>18,2</t>
+          <t>24,2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -720,7 +716,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -732,17 +728,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18,6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -754,17 +750,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>16,4</t>
+          <t>22,4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -776,17 +772,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>24,1</t>
+          <t>21,7</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -798,17 +794,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>26,9</t>
+          <t>19,6</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -820,7 +816,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26,6</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -830,7 +826,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -842,17 +838,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>26,8</t>
+          <t>33,6</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -864,17 +860,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>17,2</t>
+          <t>22,1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -886,17 +882,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>18,3</t>
+          <t>22,7</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -908,12 +904,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20,8</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -930,7 +926,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20,8</t>
+          <t>26,4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -952,17 +948,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20,2</t>
+          <t>25,4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -974,17 +970,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>25,3</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -1001,12 +997,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -1018,17 +1014,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>25,1</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -1040,12 +1036,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20,8</t>
+          <t>25,4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1062,12 +1058,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>24,3</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1084,7 +1080,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>29,9</t>
+          <t>31,6</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1094,7 +1090,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1102,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>21,4</t>
+          <t>25,7</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1116,7 +1112,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -1128,17 +1124,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>23,9</t>
+          <t>24,1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -1150,17 +1146,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22,9</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -464,17 +464,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24,4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -486,12 +486,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>35,5</t>
+          <t>37,2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -508,17 +508,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>34,1</t>
+          <t>33,6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>39</t>
         </is>
       </c>
     </row>
@@ -530,17 +530,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>27,5</t>
+          <t>30,1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -552,17 +552,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>22,8</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -574,17 +574,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>18,6</t>
+          <t>22,9</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -596,7 +596,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>26,6</t>
+          <t>29,5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>29,9</t>
+          <t>30,7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -640,17 +640,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>23,1</t>
+          <t>23,7</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -662,17 +662,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>30,1</t>
+          <t>32,3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -684,17 +684,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>32,6</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -706,17 +706,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>24,2</t>
+          <t>27,6</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>18,6</t>
+          <t>13,9</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -750,17 +750,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>22,4</t>
+          <t>23,5</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>21,7</t>
+          <t>30,8</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>19,6</t>
+          <t>28,6</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>26,6</t>
+          <t>28,5</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -838,17 +838,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>33,6</t>
+          <t>29,7</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>22,1</t>
+          <t>17,3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>22,7</t>
+          <t>25,7</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -904,17 +904,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30,9</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -926,17 +926,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>26,4</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>25,4</t>
+          <t>22,4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>33,2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -992,7 +992,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>28,2</t>
+          <t>32,4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -1014,17 +1014,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>31,4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>25,4</t>
+          <t>28,9</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>24,3</t>
+          <t>24,9</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1080,17 +1080,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>31,6</t>
+          <t>31,1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>25,7</t>
+          <t>26,2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>24,1</t>
+          <t>26,8</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1146,17 +1146,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>22,9</t>
+          <t>27,2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -447,12 +447,12 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>24,4</t>
+          <t>29,2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -474,7 +474,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -486,17 +486,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>37,2</t>
+          <t>32,3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>33,6</t>
+          <t>35,9</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -530,12 +530,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>30,1</t>
+          <t>29,5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26,9</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -574,12 +574,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>22,9</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>29,5</t>
+          <t>29,7</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>30,7</t>
+          <t>30,9</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>23,7</t>
+          <t>27,8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -662,17 +662,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>32,3</t>
+          <t>34,4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -684,17 +684,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>32,6</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -706,12 +706,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>27,6</t>
+          <t>25,9</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -728,17 +728,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>13,9</t>
+          <t>18,3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -750,12 +750,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>23,5</t>
+          <t>26,7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -772,17 +772,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>30,8</t>
+          <t>30,5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>28,6</t>
+          <t>29,3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>28,5</t>
+          <t>27,6</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>29,7</t>
+          <t>30,4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>17,3</t>
+          <t>25,7</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>25,7</t>
+          <t>28,5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>30,9</t>
+          <t>30,3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29,1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -948,17 +948,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>22,4</t>
+          <t>25,8</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -970,17 +970,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>33,2</t>
+          <t>33,8</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -992,17 +992,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>32,4</t>
+          <t>31,2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>31,4</t>
+          <t>33,1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>28,9</t>
+          <t>27,5</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -1058,17 +1058,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>24,9</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -1080,17 +1080,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>31,1</t>
+          <t>31,6</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>26,2</t>
+          <t>26,7</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1124,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>26,8</t>
+          <t>25,9</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>27,2</t>
+          <t>28,9</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -444,15 +444,19 @@
           <t>ADANA</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>HATA</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -464,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>29,2</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -486,7 +490,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>32,3</t>
+          <t>32,9</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -508,12 +512,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>35,9</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -530,17 +534,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>29,5</t>
+          <t>33,3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -552,12 +556,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26,9</t>
+          <t>29,7</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -574,17 +578,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29,9</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -596,17 +600,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>29,7</t>
+          <t>31,7</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -618,17 +622,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>30,9</t>
+          <t>31,2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -645,12 +649,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -662,12 +666,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>34,4</t>
+          <t>36,7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -684,7 +688,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>35,9</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -694,7 +698,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -706,7 +710,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>25,9</t>
+          <t>28,2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -716,7 +720,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -728,7 +732,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>18,3</t>
+          <t>24,2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -738,7 +742,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -750,7 +754,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>26,7</t>
+          <t>30,1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -760,7 +764,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -772,7 +776,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>30,5</t>
+          <t>34,5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -794,7 +798,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>29,3</t>
+          <t>30,7</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -804,7 +808,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -816,7 +820,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>27,6</t>
+          <t>30,2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -826,7 +830,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -838,7 +842,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>30,4</t>
+          <t>32,7</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -848,7 +852,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -860,7 +864,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>25,7</t>
+          <t>27,7</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -870,7 +874,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -882,17 +886,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>28,5</t>
+          <t>30,7</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -904,7 +908,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>30,3</t>
+          <t>31,7</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -914,7 +918,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -926,12 +930,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>29,1</t>
+          <t>32,4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -948,12 +952,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>25,8</t>
+          <t>29,6</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -970,7 +974,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>33,8</t>
+          <t>35,5</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -980,7 +984,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -992,7 +996,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>31,2</t>
+          <t>32,7</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1002,7 +1006,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1018,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>33,1</t>
+          <t>35,1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1024,7 +1028,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -1036,17 +1040,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>27,5</t>
+          <t>29,7</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1062,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27,3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1080,17 +1084,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>31,6</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -1102,17 +1106,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>26,7</t>
+          <t>26,2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1128,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>25,9</t>
+          <t>26,6</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1146,17 +1150,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>28,9</t>
+          <t>31,5</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -444,19 +444,15 @@
           <t>ADANA</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>HATA</t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -468,17 +464,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>30,5</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>30</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>32</t>
         </is>
       </c>
     </row>
@@ -490,17 +486,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>32,9</t>
+          <t>31,3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -512,17 +508,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>38,5</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -539,12 +535,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -566,7 +562,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -578,17 +574,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>29,9</t>
+          <t>27,6</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -600,7 +596,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>31,7</t>
+          <t>31,6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -610,7 +606,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -622,17 +618,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>31,2</t>
+          <t>31,1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -644,7 +640,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>27,8</t>
+          <t>28,1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -654,7 +650,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -666,17 +662,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>36,7</t>
+          <t>36,6</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -688,7 +684,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>35,9</t>
+          <t>36,8</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -698,7 +694,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
     </row>
@@ -710,17 +706,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>28,2</t>
+          <t>28,1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -732,17 +728,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>24,2</t>
+          <t>24,4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -754,17 +750,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>30,1</t>
+          <t>31,4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -774,19 +770,15 @@
           <t>GAZİANTEP</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>34,5</t>
-        </is>
-      </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -798,12 +790,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>30,7</t>
+          <t>32,9</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -820,12 +812,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>30,2</t>
+          <t>30,6</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -842,12 +834,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>32,7</t>
+          <t>34,6</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -864,17 +856,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>27,7</t>
+          <t>29,3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -886,7 +878,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>30,7</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -908,17 +900,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>31,7</t>
+          <t>32,2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -930,7 +922,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>32,4</t>
+          <t>31,1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -940,7 +932,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -952,12 +944,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>29,6</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -974,17 +966,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>35,5</t>
+          <t>36,6</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -996,12 +988,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>32,7</t>
+          <t>32,9</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1018,17 +1010,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>35,1</t>
+          <t>35,8</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -1040,17 +1032,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>29,7</t>
+          <t>29,9</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -1062,12 +1054,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>27,3</t>
+          <t>27,6</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1084,7 +1076,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>37,8</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1106,7 +1098,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>26,2</t>
+          <t>26,7</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1128,12 +1120,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>26,6</t>
+          <t>26,8</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1150,17 +1142,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>31,5</t>
+          <t>31,8</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>31</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -447,12 +447,12 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>30,5</t>
+          <t>31,3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -486,17 +486,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31,3</t>
+          <t>31,4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -508,12 +508,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>38,5</t>
+          <t>37,2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -530,7 +530,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>33,3</t>
+          <t>30,5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -552,17 +552,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>29,7</t>
+          <t>28,1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>27,6</t>
+          <t>26,8</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -584,7 +584,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -596,7 +596,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>31,6</t>
+          <t>31,8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -618,17 +618,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>31,1</t>
+          <t>30,3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>28,1</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -662,12 +662,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>36,6</t>
+          <t>36,7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>36,8</t>
+          <t>38,1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -706,17 +706,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>28,1</t>
+          <t>27,2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -728,17 +728,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>24,4</t>
+          <t>25,6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>31,4</t>
+          <t>30,7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,11 @@
           <t>GAZİANTEP</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>35,8</t>
+        </is>
+      </c>
       <c r="C17" t="inlineStr">
         <is>
           <t>21</t>
@@ -778,7 +782,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -790,7 +794,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>32,9</t>
+          <t>31,6</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -812,17 +816,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>30,6</t>
+          <t>29,1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -834,7 +838,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>34,6</t>
+          <t>32,7</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -844,7 +848,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -856,17 +860,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>29,3</t>
+          <t>30,1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -878,7 +882,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29,9</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -900,17 +904,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>32,2</t>
+          <t>29,8</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -922,17 +926,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>31,1</t>
+          <t>29,9</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -944,17 +948,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30,5</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -966,7 +970,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>36,6</t>
+          <t>35,3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -976,7 +980,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -988,7 +992,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>32,9</t>
+          <t>33,1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -998,7 +1002,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -1010,17 +1014,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>35,8</t>
+          <t>35,3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1036,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>29,9</t>
+          <t>28,8</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -1054,17 +1058,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>27,6</t>
+          <t>26,7</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1080,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>37,8</t>
+          <t>37,7</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1098,17 +1102,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>26,7</t>
+          <t>26,9</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -1120,12 +1124,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>26,8</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1142,17 +1146,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>31,8</t>
+          <t>33,1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -447,12 +447,12 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>31,3</t>
+          <t>31,1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -474,7 +474,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -486,17 +486,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31,4</t>
+          <t>29,9</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>37,2</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -530,17 +530,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>30,5</t>
+          <t>29,7</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>28,1</t>
+          <t>26,6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -574,12 +574,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>26,8</t>
+          <t>24,7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>31,8</t>
+          <t>30,1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -618,17 +618,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>30,3</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -662,17 +662,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>36,7</t>
+          <t>31,7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>38,1</t>
+          <t>37,1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -706,17 +706,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>27,2</t>
+          <t>26,2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>25,6</t>
+          <t>27,5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -750,17 +750,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>30,7</t>
+          <t>28,2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>35,8</t>
+          <t>34,9</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -794,12 +794,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>31,6</t>
+          <t>30,2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>29,1</t>
+          <t>27,8</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>32,7</t>
+          <t>35,3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -860,17 +860,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>30,1</t>
+          <t>29,6</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>29,9</t>
+          <t>29,3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -904,17 +904,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>29,8</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -926,17 +926,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>29,9</t>
+          <t>29,6</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -948,17 +948,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>30,5</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -970,17 +970,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>35,3</t>
+          <t>33,4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -992,7 +992,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>33,1</t>
+          <t>32,6</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -1014,17 +1014,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>35,3</t>
+          <t>33,9</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -1036,17 +1036,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>28,8</t>
+          <t>28,5</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -1058,17 +1058,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>26,7</t>
+          <t>27,3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -1085,12 +1085,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>26,9</t>
+          <t>29,3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1124,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -1146,17 +1146,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>33,1</t>
+          <t>30,2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -447,12 +447,12 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>31,1</t>
+          <t>29,6</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -474,7 +474,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -486,17 +486,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>29,9</t>
+          <t>30,3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35,3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -530,17 +530,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>29,7</t>
+          <t>31,8</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -552,17 +552,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26,6</t>
+          <t>27,5</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -574,17 +574,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>24,7</t>
+          <t>27,8</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -596,17 +596,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>30,1</t>
+          <t>31,4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -618,17 +618,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>29,9</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>30</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>35</t>
         </is>
       </c>
     </row>
@@ -640,17 +640,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27,4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -662,7 +662,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>31,7</t>
+          <t>33,6</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -684,17 +684,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>37,1</t>
+          <t>37,4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>26,2</t>
+          <t>29,1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -728,17 +728,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>27,5</t>
+          <t>26,3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>28,2</t>
+          <t>28,9</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>34,9</t>
+          <t>35,2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>30,2</t>
+          <t>30,8</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -816,17 +816,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>27,8</t>
+          <t>27,5</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -838,12 +838,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>35,3</t>
+          <t>33,4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -860,17 +860,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>29,6</t>
+          <t>27,6</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>29,3</t>
+          <t>28,6</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -904,17 +904,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>31,6</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
           <t>29</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>35</t>
         </is>
       </c>
     </row>
@@ -926,17 +926,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>29,6</t>
+          <t>31,5</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -948,17 +948,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>28,8</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -970,17 +970,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>33,4</t>
+          <t>33,2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -992,17 +992,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>32,6</t>
+          <t>32,5</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>33,9</t>
+          <t>32,5</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1036,17 +1036,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>28,5</t>
+          <t>29,9</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -1058,17 +1058,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>27,3</t>
+          <t>27,6</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1102,17 +1102,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>29,3</t>
+          <t>26,4</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1124,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>27,1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
           <t>25</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>27</t>
         </is>
       </c>
     </row>
@@ -1146,17 +1146,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>30,2</t>
+          <t>30,7</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30</t>
         </is>
       </c>
     </row>
